--- a/ClientExcel/Game/Scene.xlsx
+++ b/ClientExcel/Game/Scene.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Scene" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>#</t>
   </si>
@@ -38,9 +38,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>AssetName</t>
-  </si>
-  <si>
     <t>AssetId</t>
   </si>
   <si>
@@ -50,16 +47,13 @@
     <t>Int32</t>
   </si>
   <si>
-    <t>String</t>
-  </si>
-  <si>
     <t>场景编号</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>资源名称</t>
+    <t>场景编号枚举名</t>
   </si>
   <si>
     <t>资源编号</t>
@@ -90,7 +84,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +95,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -567,142 +567,145 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1054,14 +1057,12 @@
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1069,16 +1070,14 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1086,19 +1085,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="2:6">
@@ -1106,10 +1105,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="E5" s="1">
         <v>101</v>
@@ -1123,10 +1122,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="E6" s="1">
         <v>102</v>
